--- a/attendance_history/Present_2026-03-30.xlsx
+++ b/attendance_history/Present_2026-03-30.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -475,25 +475,79 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>AJUNA WILLFRED (99%)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2023-08-22274</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>11:51:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>mwesigwa rebecca (93%)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-24140</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>11:37:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>TUSUBIRA CALEBU (92%)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2023-08-16868</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Bcs</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0:00:01</t>
         </is>
